--- a/Side Bar Files/GWD Data/Hydrants.xlsx
+++ b/Side Bar Files/GWD Data/Hydrants.xlsx
@@ -423,8 +423,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -443,7 +447,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -858,7 +864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDBFCCF-C272-4964-86E4-4EA58A2BB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C1A4E6-40CC-42A3-8B7F-6A7FFA7FB9A7}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Hydrants.xlsx
+++ b/Side Bar Files/GWD Data/Hydrants.xlsx
@@ -9,15 +9,24 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="38">
-  <si>
-    <t>Hydrants with tap  (for common use of size 0.8 x 0.5 m platform)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="37">
+  <si>
+    <t>Hydrants with tap (for common use of size 0.8 x 0.5 m platform)</t>
+  </si>
+  <si>
+    <t>Code</t>
   </si>
   <si>
     <r>
@@ -86,7 +95,7 @@
     </r>
   </si>
   <si>
-    <t>PVC tap (MR10048)</t>
+    <t>PVC tap</t>
   </si>
   <si>
     <t>No</t>
@@ -95,6 +104,9 @@
     <t>/E</t>
   </si>
   <si>
+    <t>MR10048</t>
+  </si>
+  <si>
     <t>25mm GI Nipple</t>
   </si>
   <si>
@@ -119,7 +131,7 @@
     <t>CPOH 15%</t>
   </si>
   <si>
-    <t xml:space="preserve">Total    </t>
+    <t xml:space="preserve">Total  </t>
   </si>
   <si>
     <t>Earth work excavation as per DSR item 2.8.1</t>
@@ -149,10 +161,10 @@
     <t>/m3</t>
   </si>
   <si>
-    <t>Cement concrete 1:2:4, 20mm with nominal size graded stone, for filling the PVC Pipe and  platform construction as per DSR item 4.1.3</t>
-  </si>
-  <si>
-    <t>Form work  as per DSR item 5.9.1</t>
+    <t>Cement concrete 1:2:4, 20mm with nominal size graded stone, for filling the PVC Pipe and platform construction as per DSR item 4.1.3</t>
+  </si>
+  <si>
+    <t>Form work as per DSR item 5.9.1</t>
   </si>
   <si>
     <r>
@@ -217,16 +229,10 @@
     <t>Sub Total</t>
   </si>
   <si>
-    <t xml:space="preserve">Total  for labour </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total   </t>
-  </si>
-  <si>
-    <t>Hydrants with tap  ( for individual families of size 0.6 X 0.3 M platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PVC tap (MR10048)</t>
+    <t xml:space="preserve">Total for labour </t>
+  </si>
+  <si>
+    <t>Hydrants with tap ( for individual families of size 0.6 X 0.3 M platform)</t>
   </si>
   <si>
     <t>Nos</t>
@@ -243,10 +249,7 @@
     </r>
   </si>
   <si>
-    <t>Earth work excavation  as per DSR item 2.8.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total   for labour </t>
+    <t xml:space="preserve">Total  for labour </t>
   </si>
 </sst>
 </file>
@@ -265,13 +268,13 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Cambria"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Cambria"/>
@@ -393,25 +396,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -420,7 +409,7 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
@@ -432,62 +421,62 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -566,6 +555,113 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="GWD DR Abstract"/>
+      <sheetName val="GWD MR Abstract"/>
+      <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
+      <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
+      <sheetName val="GI on Wall PRICE"/>
+      <sheetName val="GI wo Trench"/>
+      <sheetName val="GI With Trench PRICE"/>
+      <sheetName val="GI Works"/>
+      <sheetName val="Gravel for TWC"/>
+      <sheetName val="Gutter&amp;Clamp"/>
+      <sheetName val="HP Erection and Pullout"/>
+      <sheetName val="HP Repair Labour"/>
+      <sheetName val="HP Repair Spares"/>
+      <sheetName val="Hydrants"/>
+      <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
+      <sheetName val="Metallic PH"/>
+      <sheetName val="Motor Starter GWD"/>
+      <sheetName val="Motor Starter Monoblock"/>
+      <sheetName val="Motor Starter PRICE"/>
+      <sheetName val="Other Fittings PRICE"/>
+      <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
+      <sheetName val="Pump Erection "/>
+      <sheetName val="Pump Pullout"/>
+      <sheetName val="PVC Fittings"/>
+      <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
+      <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
+      <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
+      <sheetName val="PVC With Trench"/>
+      <sheetName val="Scaffolding"/>
+      <sheetName val="Services"/>
+      <sheetName val="TW Casing Pipes"/>
+      <sheetName val="UG Cable PRICE"/>
+      <sheetName val="Water Meter"/>
+      <sheetName val="Water Tank"/>
+      <sheetName val="Well Protection"/>
+      <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
+      <sheetName val="ZCost Index"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -864,11 +960,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C1A4E6-40CC-42A3-8B7F-6A7FFA7FB9A7}">
-  <dimension ref="A1:G52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8359425-9000-4F0D-9B3A-1FC7647ABAA6}">
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="12.75">
+    <row r="1" spans="1:8" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -878,474 +974,504 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" ht="12.75">
-      <c r="A2" s="4">
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="12.75">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="C2" s="4">
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5">
         <v>110</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5">
         <v>170</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="F2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="7">
         <f>C2*E2/100</f>
         <v>187</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="12.75">
-      <c r="A3" s="4">
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="12.75">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
+        <v>150</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>65</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4">
-        <v>150</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4">
-        <v>65</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <f>C3*E3/100</f>
         <v>97.50</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="12.75">
-      <c r="A4" s="4">
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="12.75">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5">
+        <f t="array" ref="E4">IFERROR(INDEX(LMRRates,MATCH(H4,LMRCodes,0),),)</f>
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="F4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="7">
         <f>C4*E4</f>
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="12.75">
-      <c r="A5" s="4">
+      <c r="H4" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="12.75">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5">
+        <v>40</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4">
-        <v>40</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <f>C5*E5</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="12.75">
-      <c r="A6" s="4">
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" ht="12.75">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4">
+      <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="5">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5">
         <v>45</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="7">
         <f>C6*E6</f>
         <v>90</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="12.75">
-      <c r="A7" s="4">
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="12.75">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="5">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5">
         <v>45</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="F7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="7">
         <f>C7*E7</f>
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="12.75">
-      <c r="A8" s="4">
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" ht="12.75">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5">
         <v>55</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="F8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7">
         <f>C8*E8</f>
         <v>55</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="12.75">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="6">
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="12.75">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="7">
         <f>SUM(G2:G8)</f>
         <v>578.50</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="12.75">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6">
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" ht="12.75">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="7">
         <f>G9*0.01</f>
         <v>5.785</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="12.75">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="6">
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" ht="12.75">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="7">
         <f>SUM(G9:G10)</f>
         <v>584.285</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="12.75">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="6">
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" ht="12.75">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="7">
         <f>G11*15%</f>
         <v>87.642750000000007</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="12.75">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="7">
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" ht="12.75">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="8">
         <f>ROUND(SUM(G11:G12),2)</f>
         <v>671.93</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="12.75">
-      <c r="A14" s="4">
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" ht="12.75">
+      <c r="A14" s="5">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="4">
+      <c r="B14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="5">
         <v>0.10</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="5">
         <v>249.03</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="F14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="7">
         <f>C14*E14</f>
         <v>24.902999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="12.75">
-      <c r="A15" s="4">
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="12.75">
+      <c r="A15" s="5">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="4">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <v>6393.89</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="F15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="7">
         <f>C15*E15</f>
         <v>933.50793999999996</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="12.75">
-      <c r="A16" s="4">
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="12.75">
+      <c r="A16" s="5">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4">
+      <c r="B16" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="5">
         <f>2*(0.8+0.5)*0.1</f>
         <v>0.26</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="5">
         <v>267.33</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="F16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="7">
         <f>C16*E16</f>
         <v>69.505799999999994</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="12.75">
-      <c r="A17" s="4">
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="12.75">
+      <c r="A17" s="5">
         <v>11</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="B17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="5">
         <f>0.8*0.5+C16</f>
         <v>0.66</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="5">
         <v>255.98</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="6">
+      <c r="F17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="7">
         <f>C17*E17</f>
         <v>168.9468</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="12.75">
-      <c r="A18" s="9">
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="12.75">
+      <c r="A18" s="10">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="B18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5">
         <v>0.22</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="5">
         <v>784</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="F18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="7">
         <f>C18*E18</f>
         <v>172.48</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="12.75">
-      <c r="A19" s="10"/>
-      <c r="B19" s="5" t="s">
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="12.75">
+      <c r="A19" s="11"/>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="4">
-        <v>0.22</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <v>645</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="F19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="7">
         <f>C19*E19</f>
         <v>141.90</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="12.75">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="6">
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="12.75">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="7">
         <f>SUM(G18:G19)</f>
         <v>314.38</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="12.75">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="6">
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" ht="12.75">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="7">
         <f>G20*0.01</f>
         <v>3.1438000000000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="12.75">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="6">
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" ht="12.75">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="7">
         <f>SUM(G20:G21)</f>
         <v>317.52379999999999</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="12.75">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="6">
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" ht="12.75">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="7">
         <f>G22*15%</f>
         <v>47.628570000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="12.75">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="6">
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" ht="12.75">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="7">
         <f>SUM(G22:G23)</f>
         <v>365.15237000000002</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="12.75">
-      <c r="A25" s="4"/>
-      <c r="B25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="7">
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="12.75">
+      <c r="A25" s="5"/>
+      <c r="B25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="8">
         <f>ROUND(G14+G15+G16+G17+G24,2)</f>
         <v>1562.02</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="12.75">
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" ht="12.75">
       <c r="A26" s="1" t="str">
         <f>CONCATENATE("Say ₹ ",G13," + ",G25," x Cost Index")</f>
         <v>Say ₹ 671.93 + 1562.02 x Cost Index</v>
@@ -1356,10 +1482,11 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" ht="12.75">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="12.75">
       <c r="A27" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1367,470 +1494,498 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" ht="12.75">
-      <c r="A28" s="13">
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28" spans="1:8" ht="12.75">
+      <c r="A28" s="14">
         <v>1</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" s="13">
+      <c r="B28" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="14">
         <v>110</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="13">
+      <c r="D28" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
         <v>170</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="F28" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="16">
         <f>C28*E28/100</f>
         <v>187</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="12.75">
-      <c r="A29" s="13">
+      <c r="H28" s="16"/>
+    </row>
+    <row r="29" spans="1:8" ht="12.75">
+      <c r="A29" s="14">
         <v>2</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="14">
+        <v>150</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="14">
+        <v>65</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="13">
-        <v>150</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="13">
-        <v>65</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="15">
+      <c r="G29" s="16">
         <f>C29*E29/100</f>
         <v>97.50</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="12.75">
-      <c r="A30" s="13">
+      <c r="H29" s="16"/>
+    </row>
+    <row r="30" spans="1:8" ht="12.75">
+      <c r="A30" s="14">
         <v>3</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="13">
+      <c r="B30" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="13">
+      <c r="D30" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="14">
+        <f t="array" ref="E30">IFERROR(INDEX(LMRRates,MATCH(H30,LMRCodes,0),),)</f>
         <v>64</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="15">
+      <c r="F30" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="16">
         <f>C30*E30</f>
         <v>64</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="12.75">
-      <c r="A31" s="13">
+      <c r="H30" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="12.75">
+      <c r="A31" s="14">
         <v>4</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="14">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="13">
-        <v>1</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="13">
-        <v>40</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" s="15">
+      <c r="G31" s="16">
         <f>C31*E31</f>
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="12.75">
-      <c r="A32" s="13">
+      <c r="H31" s="16"/>
+    </row>
+    <row r="32" spans="1:8" ht="12.75">
+      <c r="A32" s="14">
         <v>5</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="13">
+      <c r="B32" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="14">
         <v>2</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="14">
         <v>45</v>
       </c>
-      <c r="F32" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="15">
+      <c r="F32" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="16">
         <f>C32*E32</f>
         <v>90</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="12.75">
-      <c r="A33" s="13">
+      <c r="H32" s="16"/>
+    </row>
+    <row r="33" spans="1:8" ht="12.75">
+      <c r="A33" s="14">
         <v>6</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="13">
+      <c r="D33" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="14">
         <v>45</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="15">
+      <c r="F33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="16">
         <f>C33*E33</f>
         <v>45</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="12.75">
-      <c r="A34" s="13">
+      <c r="H33" s="16"/>
+    </row>
+    <row r="34" spans="1:8" ht="12.75">
+      <c r="A34" s="14">
         <v>7</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="13">
+      <c r="B34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="14">
         <v>1</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13">
+      <c r="D34" s="14"/>
+      <c r="E34" s="14">
         <v>55</v>
       </c>
-      <c r="F34" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="15">
+      <c r="F34" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="16">
         <f>C34*E34</f>
         <v>55</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="12.75">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="15">
+      <c r="H34" s="16"/>
+    </row>
+    <row r="35" spans="1:8" ht="12.75">
+      <c r="A35" s="14"/>
+      <c r="B35" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="16">
         <f>SUM(G28:G34)</f>
         <v>578.50</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="12.75">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="15">
+      <c r="H35" s="16"/>
+    </row>
+    <row r="36" spans="1:8" ht="12.75">
+      <c r="A36" s="14"/>
+      <c r="B36" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="16">
         <f>G35*0.01</f>
         <v>5.785</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="12.75">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="15">
+      <c r="H36" s="16"/>
+    </row>
+    <row r="37" spans="1:8" ht="12.75">
+      <c r="A37" s="14"/>
+      <c r="B37" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="16">
         <f>SUM(G35:G36)</f>
         <v>584.285</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="12.75">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="15">
+      <c r="H37" s="16"/>
+    </row>
+    <row r="38" spans="1:8" ht="12.75">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="16">
         <f>G37*15%</f>
         <v>87.642750000000007</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="12.75">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="16">
+      <c r="H38" s="16"/>
+    </row>
+    <row r="39" spans="1:8" ht="12.75">
+      <c r="A39" s="14"/>
+      <c r="B39" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="17">
         <f>ROUND(SUM(G37:G38),2)</f>
         <v>671.93</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="12.75">
-      <c r="A40" s="13">
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40" spans="1:8" ht="12.75">
+      <c r="A40" s="14">
         <v>8</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="13">
+      <c r="B40" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="14">
         <v>0.053999999999999999</v>
       </c>
-      <c r="D40" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="13">
+      <c r="D40" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="14">
         <v>249.03</v>
       </c>
-      <c r="F40" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G40" s="15">
+      <c r="F40" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="16">
         <f>C40*E40</f>
         <v>13.447620000000001</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="12.75">
-      <c r="A41" s="13">
+      <c r="H40" s="16"/>
+    </row>
+    <row r="41" spans="1:8" ht="12.75">
+      <c r="A41" s="14">
         <v>9</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0.08</v>
+      </c>
+      <c r="D41" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="13">
-        <v>0.08</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="17">
+      <c r="E41" s="18">
         <v>6393.89</v>
       </c>
-      <c r="F41" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" s="15">
+      <c r="F41" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="16">
         <f>C41*E41</f>
         <v>511.51119999999997</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="12.75">
-      <c r="A42" s="13">
+      <c r="H41" s="16"/>
+    </row>
+    <row r="42" spans="1:8" ht="12.75">
+      <c r="A42" s="14">
         <v>10</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="13">
+      <c r="B42" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="14">
         <v>0.18</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" s="13">
+      <c r="D42" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="14">
         <v>267.33</v>
       </c>
-      <c r="F42" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G42" s="15">
+      <c r="F42" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="16">
         <f>C42*E42</f>
         <v>48.119399999999999</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="12.75">
-      <c r="A43" s="13">
+      <c r="H42" s="16"/>
+    </row>
+    <row r="43" spans="1:8" ht="12.75">
+      <c r="A43" s="14">
         <v>11</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0.36</v>
+      </c>
+      <c r="D43" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="13">
-        <v>0.36</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" s="13">
+      <c r="E43" s="14">
         <v>255.98</v>
       </c>
-      <c r="F43" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="18">
+      <c r="F43" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="19">
         <f>C43*E43</f>
         <v>92.152799999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="12.75">
-      <c r="A44" s="19">
+      <c r="H43" s="19"/>
+    </row>
+    <row r="44" spans="1:8" ht="12.75">
+      <c r="A44" s="20">
         <v>12</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C44" s="13">
+      <c r="B44" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="14">
         <v>0.22</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44" s="14">
         <v>784</v>
       </c>
-      <c r="F44" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G44" s="15">
+      <c r="F44" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="16">
         <f>C44*E44</f>
         <v>172.48</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="12.75">
-      <c r="A45" s="10"/>
-      <c r="B45" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="13">
+      <c r="H44" s="16"/>
+    </row>
+    <row r="45" spans="1:8" ht="12.75">
+      <c r="A45" s="11"/>
+      <c r="B45" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="14">
         <v>0.22</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45" s="14">
         <v>645</v>
       </c>
-      <c r="F45" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="15">
+      <c r="F45" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="16">
         <f>C45*E45</f>
         <v>141.90</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="12.75">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="15">
+      <c r="H45" s="16"/>
+    </row>
+    <row r="46" spans="1:8" ht="12.75">
+      <c r="A46" s="14"/>
+      <c r="B46" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="16">
         <f>SUM(G44:G45)</f>
         <v>314.38</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="12.75">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="15">
+      <c r="H46" s="16"/>
+    </row>
+    <row r="47" spans="1:8" ht="12.75">
+      <c r="A47" s="14"/>
+      <c r="B47" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="16">
         <f>G46*0.01</f>
         <v>3.1438000000000001</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="12.75">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="15">
+      <c r="H47" s="16"/>
+    </row>
+    <row r="48" spans="1:8" ht="12.75">
+      <c r="A48" s="14"/>
+      <c r="B48" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="16">
         <f>SUM(G46:G47)</f>
         <v>317.52379999999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="12.75">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="15">
+      <c r="H48" s="16"/>
+    </row>
+    <row r="49" spans="1:8" ht="12.75">
+      <c r="A49" s="14"/>
+      <c r="B49" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="16">
         <f>G48*15%</f>
         <v>47.628570000000003</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="12.75">
-      <c r="A50" s="13"/>
-      <c r="B50" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="15">
+      <c r="H49" s="16"/>
+    </row>
+    <row r="50" spans="1:8" ht="12.75">
+      <c r="A50" s="14"/>
+      <c r="B50" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="16">
         <f>SUM(G48:G49)</f>
         <v>365.15237000000002</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="12.75">
-      <c r="A51" s="13"/>
-      <c r="B51" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="16">
+      <c r="H50" s="16"/>
+    </row>
+    <row r="51" spans="1:8" ht="12.75">
+      <c r="A51" s="14"/>
+      <c r="B51" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="17">
         <f>ROUND(G40+G41+G42+G43+G50,2)</f>
         <v>1030.38</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="12.75">
+      <c r="H51" s="17"/>
+    </row>
+    <row r="52" spans="1:8" ht="12.75">
       <c r="A52" s="12" t="str">
         <f>CONCATENATE("Say ₹ ",G39," + ",G51," x Cost Index")</f>
         <v>Say ₹ 671.93 + 1030.38 x Cost Index</v>
@@ -1841,6 +1996,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="3"/>
+      <c r="H52" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Side Bar Files/GWD Data/Hydrants.xlsx
+++ b/Side Bar Files/GWD Data/Hydrants.xlsx
@@ -960,7 +960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8359425-9000-4F0D-9B3A-1FC7647ABAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561C55B3-8B85-4CEF-AEBA-523673E9BAA6}">
   <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/Hydrants.xlsx
+++ b/Side Bar Files/GWD Data/Hydrants.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -605,10 +605,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -960,7 +960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561C55B3-8B85-4CEF-AEBA-523673E9BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B239C1B-B30D-46C8-B45F-2405B01ABAA6}">
   <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
